--- a/scholarship_application_forms/040_student_enrolment_application_form--scholarship_application_forms.xlsx
+++ b/scholarship_application_forms/040_student_enrolment_application_form--scholarship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parent_name</t>
+          <t>parent_name_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parent Name</t>
+          <t>Parent Name 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>guardian_name</t>
+          <t>guardian_name_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Guardian Name</t>
+          <t>Guardian Name 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>student_enrolment</t>
+          <t>student_enrolment_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Student Enrolment</t>
+          <t>Student Enrolment 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>student_enrolment_choices</t>
+          <t>student_enrolment_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>student_enrolment_choices</t>
+          <t>student_enrolment_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
